--- a/samples/outputs/Deals20260518T043243_HPI_Uplift_parsed.xlsx
+++ b/samples/outputs/Deals20260518T043243_HPI_Uplift_parsed.xlsx
@@ -114,6 +114,9 @@
     <x:t>HP USB-C Dock G5</x:t>
   </x:si>
   <x:si>
+    <x:t>Max Qty: 100</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
@@ -141,6 +144,9 @@
     <x:t>HP EB8G1I14 U5 225U 14 16GB/512 PC</x:t>
   </x:si>
   <x:si>
+    <x:t>Max Qty: 500</x:t>
+  </x:si>
+  <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
@@ -148,6 +154,9 @@
   </x:si>
   <x:si>
     <x:t>HP ZB8G1i14 U5 225H 14 16GB/512 PC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Max Qty: 250</x:t>
   </x:si>
   <x:si>
     <x:t>*</x:t>
@@ -613,13 +622,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>165.83</x:v>
       </x:c>
       <x:c r="K3" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="W3" s="0">
         <x:v>1</x:v>
@@ -627,25 +639,28 @@
     </x:row>
     <x:row r="4" spans="1:27">
       <x:c r="A4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>336.7</x:v>
       </x:c>
       <x:c r="K4" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="W4" s="0">
         <x:v>1</x:v>
@@ -653,25 +668,28 @@
     </x:row>
     <x:row r="5" spans="1:27">
       <x:c r="A5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>3393.88</x:v>
       </x:c>
       <x:c r="K5" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="W5" s="0">
         <x:v>1</x:v>
@@ -679,25 +697,28 @@
     </x:row>
     <x:row r="6" spans="1:27">
       <x:c r="A6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>500</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>2258.18</x:v>
       </x:c>
       <x:c r="K6" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="W6" s="0">
         <x:v>1</x:v>
@@ -705,25 +726,28 @@
     </x:row>
     <x:row r="7" spans="1:27">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>250</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>2160</x:v>
       </x:c>
       <x:c r="K7" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="R7" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W7" s="0">
         <x:v>1</x:v>
@@ -731,10 +755,10 @@
     </x:row>
     <x:row r="8" spans="1:27">
       <x:c r="B8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
